--- a/src/test/resources/excel/menuAdministrador/datosMenuAdministrador.xlsx
+++ b/src/test/resources/excel/menuAdministrador/datosMenuAdministrador.xlsx
@@ -1,31 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\automatizacion\portal Famisanar\src\test\resources\excel\menuAdministrador\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C710C958-C39D-4095-8B16-04D2BFCD35EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="16980" windowHeight="7740" activeTab="1"/>
+    <workbookView minimized="1" xWindow="15" yWindow="15" windowWidth="20460" windowHeight="11490" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="4" r:id="rId1"/>
     <sheet name="menuUsuarios" sheetId="1" r:id="rId2"/>
     <sheet name="menuInformes" sheetId="5" r:id="rId3"/>
-    <sheet name="Administrar aplicaciones" sheetId="6" r:id="rId4"/>
+    <sheet name="AdministrarAplicaciones" sheetId="6" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="108">
   <si>
     <t>52102459</t>
   </si>
   <si>
     <t>CC</t>
-  </si>
-  <si>
-    <t>3456789</t>
   </si>
   <si>
     <t>Usuario</t>
@@ -159,21 +175,6 @@
     <t xml:space="preserve">Tipo Novedad </t>
   </si>
   <si>
-    <t xml:space="preserve">Fecha Inicial </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fecha Final </t>
-  </si>
-  <si>
-    <t>VISITA</t>
-  </si>
-  <si>
-    <t>Informes Usuarios -&gt; Log Usuarios</t>
-  </si>
-  <si>
-    <t>Informes Usuarios -&gt; Log Actividad</t>
-  </si>
-  <si>
     <t>Aplicación</t>
   </si>
   <si>
@@ -186,15 +187,6 @@
     <t>Nombre Aplicación debe existir en el Portal</t>
   </si>
   <si>
-    <t>Informes Usuarios -&gt; Usuarios por App por Menú</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Informes Usuarios -&gt; Usuarios por App por Menú por Filtro </t>
-  </si>
-  <si>
-    <t>Informes Usuarios -&gt; Usuarios por App por Menú por Filtro por Grupo</t>
-  </si>
-  <si>
     <t>Menú</t>
   </si>
   <si>
@@ -216,18 +208,9 @@
     <t>Lista desplegable, permite seleccionar CONEXION o VISITA</t>
   </si>
   <si>
-    <t>Se debe mantener el formato estipulado aaaa/mm/dd</t>
-  </si>
-  <si>
-    <t>Creación De Aplicación</t>
-  </si>
-  <si>
     <t>Modificación De Aplicación</t>
   </si>
   <si>
-    <t>Datos Ingreso Portal</t>
-  </si>
-  <si>
     <t>Nombre</t>
   </si>
   <si>
@@ -240,9 +223,6 @@
     <t>Portal Automatizado En Modificacion</t>
   </si>
   <si>
-    <t xml:space="preserve"> Usuario</t>
-  </si>
-  <si>
     <t>Descripción</t>
   </si>
   <si>
@@ -252,9 +232,6 @@
     <t>Prueba automatizacion en entorno QA Modificado</t>
   </si>
   <si>
-    <t>Clave</t>
-  </si>
-  <si>
     <t>Servidor</t>
   </si>
   <si>
@@ -273,12 +250,6 @@
     <t>/redservicios</t>
   </si>
   <si>
-    <t>01/12/23</t>
-  </si>
-  <si>
-    <t>15/12/23</t>
-  </si>
-  <si>
     <t>ROJAS</t>
   </si>
   <si>
@@ -297,9 +268,6 @@
     <t>3</t>
   </si>
   <si>
-    <t>FAMI1234</t>
-  </si>
-  <si>
     <t>r.lizarazo@praxisglobe.net</t>
   </si>
   <si>
@@ -363,20 +331,80 @@
     <t>Lizarazo</t>
   </si>
   <si>
-    <t>ROJAS RONCANCIO ROBERTO CARLOS</t>
-  </si>
-  <si>
-    <t>CC 1079742311</t>
+    <t>ROJAS LIZARAZO ROBERTO CARLOS</t>
+  </si>
+  <si>
+    <t>Log Usuarios</t>
+  </si>
+  <si>
+    <t>pepito</t>
+  </si>
+  <si>
+    <t>Dia inicio</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mes inicio </t>
+  </si>
+  <si>
+    <t>Año inicio</t>
+  </si>
+  <si>
+    <t>Dia fin</t>
+  </si>
+  <si>
+    <t>Mes fin</t>
+  </si>
+  <si>
+    <t>Año fin</t>
+  </si>
+  <si>
+    <t>septiembre</t>
+  </si>
+  <si>
+    <t>2024</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Log  Actividad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usuarios Por Aplicación </t>
+  </si>
+  <si>
+    <t>Usuarios por App por Menú</t>
+  </si>
+  <si>
+    <t>Usuarios por App por Menú por Filtro</t>
+  </si>
+  <si>
+    <t>Administador Solicitudes</t>
+  </si>
+  <si>
+    <t>Usuarios por App por Menú por Filtro por Grupo</t>
+  </si>
+  <si>
+    <t>1079742321</t>
+  </si>
+  <si>
+    <t>CC 1079742321</t>
+  </si>
+  <si>
+    <t>Administrar Aplicaciones</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -467,6 +495,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -667,7 +701,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -687,9 +721,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -697,7 +729,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="3" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="3" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -710,10 +741,6 @@
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -729,9 +756,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -755,25 +779,33 @@
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="3" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="3" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="3" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -784,12 +816,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -804,7 +830,6 @@
     <xf numFmtId="49" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="20% - Énfasis1" xfId="3" builtinId="30"/>
@@ -813,7 +838,532 @@
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="59">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <border outline="0">
         <left style="thin">
@@ -850,7 +1400,7 @@
         <name val="Calibri"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border outline="0">
@@ -888,7 +1438,7 @@
         <name val="Calibri"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border outline="0">
@@ -926,7 +1476,7 @@
         <name val="Calibri"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
@@ -1012,7 +1562,7 @@
         <name val="Calibri"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1070,7 +1620,7 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right style="thin">
@@ -1118,7 +1668,7 @@
         <name val="Calibri"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border outline="0">
@@ -1153,11 +1703,11 @@
         <name val="Calibri"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
-  <tableStyles count="1" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Estilo de tabla 1" pivot="0" count="0"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Estilo de tabla 1" pivot="0" count="0" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1171,81 +1721,189 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="login" displayName="login" ref="A1:C4" totalsRowShown="0" headerRowDxfId="23" headerRowBorderDxfId="22" tableBorderDxfId="21" headerRowCellStyle="Énfasis1">
-  <autoFilter ref="A1:C4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="login" displayName="login" ref="A1:C4" totalsRowShown="0" headerRowDxfId="58" headerRowBorderDxfId="57" tableBorderDxfId="56" headerRowCellStyle="Énfasis1">
+  <autoFilter ref="A1:C4" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="Inicio de Sesión Portal"/>
-    <tableColumn id="2" name="Columna1"/>
-    <tableColumn id="3" name="Columna2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Inicio de Sesión Portal"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Columna1"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Columna2"/>
+  </tableColumns>
+  <tableStyleInfo name="Estilo de tabla 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{6A98CC21-CC66-4919-AA41-D520E66CCF6C}" name="Tabla912" displayName="Tabla912" ref="M1:O11" totalsRowShown="0" headerRowDxfId="23" headerRowBorderDxfId="22" tableBorderDxfId="21" headerRowCellStyle="Énfasis1">
+  <autoFilter ref="M1:O11" xr:uid="{6A98CC21-CC66-4919-AA41-D520E66CCF6C}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{4A36624C-21A0-459A-A320-9FC42D4EB225}" name="Usuarios Por Aplicación " dataCellStyle="20% - Énfasis1"/>
+    <tableColumn id="2" xr3:uid="{5407A745-FE0B-4BC6-A411-F92645378B6D}" name="Columna1" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{FFEEB12E-559E-4028-87FE-48B986240FBD}" name="Columna2" dataDxfId="19"/>
+  </tableColumns>
+  <tableStyleInfo name="Estilo de tabla 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{2F406A86-A936-4F91-A70F-C6DD9A352FDD}" name="Tabla12" displayName="Tabla12" ref="Q1:S3" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16" totalsRowBorderDxfId="15" headerRowCellStyle="Énfasis1">
+  <autoFilter ref="Q1:S3" xr:uid="{2F406A86-A936-4F91-A70F-C6DD9A352FDD}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{E6CC880D-72CB-4E11-998F-707114F2BC12}" name="Usuarios por App por Menú"/>
+    <tableColumn id="2" xr3:uid="{61010C93-7A7D-4ABB-BEB7-7CC17455EE40}" name="Columna1"/>
+    <tableColumn id="3" xr3:uid="{597C008D-0DF9-4B2B-9753-BBCAA8E4B456}" name="Columna2"/>
+  </tableColumns>
+  <tableStyleInfo name="Estilo de tabla 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{066EBDC6-687E-4611-823A-871FFB88C896}" name="Tabla13" displayName="Tabla13" ref="U1:W4" totalsRowShown="0" headerRowDxfId="14" headerRowBorderDxfId="13" tableBorderDxfId="12" headerRowCellStyle="Énfasis1">
+  <autoFilter ref="U1:W4" xr:uid="{066EBDC6-687E-4611-823A-871FFB88C896}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{3A50E7EA-C75A-4AB3-BFAD-57AFBE5DDC70}" name="Usuarios por App por Menú por Filtro"/>
+    <tableColumn id="2" xr3:uid="{BF77EA63-B37F-46D3-860D-E02A3A57232A}" name="Columna1"/>
+    <tableColumn id="3" xr3:uid="{E74CF927-3D3E-4AA0-93E9-503DC4308BED}" name="Columna2"/>
+  </tableColumns>
+  <tableStyleInfo name="Estilo de tabla 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{6A6CF4D1-D24E-438C-B7BD-C3530132EA8B}" name="Tabla14" displayName="Tabla14" ref="Y1:AA5" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" headerRowCellStyle="Énfasis1">
+  <autoFilter ref="Y1:AA5" xr:uid="{6A6CF4D1-D24E-438C-B7BD-C3530132EA8B}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{05F9D523-9458-4CFF-B9A9-17BC1097AE2C}" name="Usuarios por App por Menú por Filtro por Grupo"/>
+    <tableColumn id="2" xr3:uid="{E55A2217-204C-4794-9FB0-79CD310B66E2}" name="Columna1"/>
+    <tableColumn id="3" xr3:uid="{2B42D31C-5430-4A88-9D52-E5EE5903E82B}" name="Columna2"/>
+  </tableColumns>
+  <tableStyleInfo name="Estilo de tabla 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{83FBA4FD-6B8B-437D-AAF9-DC107C6B3D2A}" name="Tabla716" displayName="Tabla716" ref="A1:C4" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" headerRowCellStyle="Énfasis1">
+  <autoFilter ref="A1:C4" xr:uid="{83FBA4FD-6B8B-437D-AAF9-DC107C6B3D2A}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{EBE279A7-46A5-4E95-9496-79C551A86E28}" name="Inicio de Sesión Portal"/>
+    <tableColumn id="2" xr3:uid="{DCAD1082-E7D3-42EF-AA61-1AA12D683785}" name="Columna1"/>
+    <tableColumn id="3" xr3:uid="{924A0A5F-C0C9-47D3-A285-0CB96F7CF15A}" name="Columna2"/>
+  </tableColumns>
+  <tableStyleInfo name="Estilo de tabla 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{0B188FB3-CF6B-4289-8858-4A050DF2FDA7}" name="Tabla16" displayName="Tabla16" ref="F1:H6" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4" tableBorderDxfId="3" headerRowCellStyle="Énfasis1">
+  <autoFilter ref="F1:H6" xr:uid="{0B188FB3-CF6B-4289-8858-4A050DF2FDA7}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{AA964114-0856-402F-B2C5-529DD6E773C0}" name="Administrar Aplicaciones" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{14FDF9C4-5291-424F-9FD8-E48F9402AD89}" name="Columna1" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{A52A183D-8811-4CB4-B259-732487BAC941}" name="Columna2" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="Estilo de tabla 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="solicitar_usuario" displayName="solicitar_usuario" ref="E1:G15" totalsRowShown="0" headerRowDxfId="20" headerRowBorderDxfId="19" tableBorderDxfId="18" headerRowCellStyle="Énfasis1">
-  <autoFilter ref="E1:G15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="solicitar_usuario" displayName="solicitar_usuario" ref="E1:G15" totalsRowShown="0" headerRowDxfId="55" headerRowBorderDxfId="54" tableBorderDxfId="53" headerRowCellStyle="Énfasis1">
+  <autoFilter ref="E1:G15" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="Solicitar Usuario" dataDxfId="17" dataCellStyle="20% - Énfasis1"/>
-    <tableColumn id="2" name="Columna1" dataDxfId="16"/>
-    <tableColumn id="3" name="Columna2" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Solicitar Usuario" dataDxfId="52" dataCellStyle="20% - Énfasis1"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Columna1" dataDxfId="51"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Columna2" dataDxfId="50"/>
   </tableColumns>
   <tableStyleInfo name="Estilo de tabla 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="administrar_usuario" displayName="administrar_usuario" ref="I1:K6" totalsRowShown="0" headerRowDxfId="14" headerRowBorderDxfId="13" tableBorderDxfId="12" headerRowCellStyle="Énfasis1">
-  <autoFilter ref="I1:K6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="administrar_usuario" displayName="administrar_usuario" ref="I1:K6" totalsRowShown="0" headerRowDxfId="49" headerRowBorderDxfId="48" tableBorderDxfId="47" headerRowCellStyle="Énfasis1">
+  <autoFilter ref="I1:K6" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="Administrar  Usuario" dataDxfId="11"/>
-    <tableColumn id="2" name="Columna1" dataDxfId="10"/>
-    <tableColumn id="3" name="Columna2" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Administrar  Usuario" dataDxfId="46"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Columna1" dataDxfId="45"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Columna2" dataDxfId="44"/>
   </tableColumns>
   <tableStyleInfo name="Estilo de tabla 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="administrar_solicitudes" displayName="administrar_solicitudes" ref="Y1:AA5" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" headerRowCellStyle="Énfasis1">
-  <autoFilter ref="Y1:AA5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="administrar_solicitudes" displayName="administrar_solicitudes" ref="Y1:AA5" totalsRowShown="0" headerRowDxfId="43" headerRowBorderDxfId="42" tableBorderDxfId="41" headerRowCellStyle="Énfasis1">
+  <autoFilter ref="Y1:AA5" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="Administrar  Solicitudes"/>
-    <tableColumn id="2" name="Columna1"/>
-    <tableColumn id="3" name="Columna2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Administrar  Solicitudes"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Columna1"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Columna2"/>
   </tableColumns>
   <tableStyleInfo name="Estilo de tabla 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="administrar_perfiles" displayName="administrar_perfiles" ref="M1:O10" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4" tableBorderDxfId="3" headerRowCellStyle="Énfasis1">
-  <autoFilter ref="M1:O10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="administrar_perfiles" displayName="administrar_perfiles" ref="M1:O10" totalsRowShown="0" headerRowDxfId="40" headerRowBorderDxfId="39" tableBorderDxfId="38" headerRowCellStyle="Énfasis1">
+  <autoFilter ref="M1:O10" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="Administrar  Perfiles"/>
-    <tableColumn id="2" name="Columna1"/>
-    <tableColumn id="3" name="Columna2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Administrar  Perfiles"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Columna1"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Columna2"/>
   </tableColumns>
   <tableStyleInfo name="Estilo de tabla 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Tabla6" displayName="Tabla6" ref="Q1:S5" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0" headerRowCellStyle="Énfasis1">
-  <autoFilter ref="Q1:S5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Tabla6" displayName="Tabla6" ref="Q1:S5" totalsRowShown="0" headerRowDxfId="37" headerRowBorderDxfId="36" tableBorderDxfId="35" headerRowCellStyle="Énfasis1">
+  <autoFilter ref="Q1:S5" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="Administrar  Datos Contactabilidad"/>
-    <tableColumn id="2" name="Columna1"/>
-    <tableColumn id="3" name="Columna2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Administrar  Datos Contactabilidad"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Columna1"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Columna2"/>
+  </tableColumns>
+  <tableStyleInfo name="Estilo de tabla 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{58D854AF-B684-492D-A7F7-2C4E3B4DFE61}" name="Tabla7" displayName="Tabla7" ref="A1:C4" totalsRowShown="0" headerRowDxfId="34" headerRowBorderDxfId="33" tableBorderDxfId="32" headerRowCellStyle="Énfasis1">
+  <autoFilter ref="A1:C4" xr:uid="{58D854AF-B684-492D-A7F7-2C4E3B4DFE61}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{9A0C59B9-E296-4372-94C3-172E373AE98A}" name="Inicio de Sesión Portal"/>
+    <tableColumn id="2" xr3:uid="{9258F139-80EF-45F5-96C1-C88424874BF5}" name="Columna1"/>
+    <tableColumn id="3" xr3:uid="{F2868242-455E-47D9-B8A6-3E5769279A82}" name="Columna2"/>
+  </tableColumns>
+  <tableStyleInfo name="Estilo de tabla 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{22E3684A-5EEC-4567-A610-2AB4C264E59E}" name="Tabla8" displayName="Tabla8" ref="E1:G4" totalsRowShown="0" headerRowDxfId="31" headerRowBorderDxfId="30" tableBorderDxfId="29" headerRowCellStyle="Énfasis1">
+  <autoFilter ref="E1:G4" xr:uid="{22E3684A-5EEC-4567-A610-2AB4C264E59E}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{819FD433-4D5A-4CA0-B86E-C6FCF0719B05}" name="Log Usuarios"/>
+    <tableColumn id="2" xr3:uid="{1E9D15A7-BDEE-4052-BF25-B1C36F073044}" name="Columna1"/>
+    <tableColumn id="3" xr3:uid="{847A426F-E07F-409E-ACA3-566E2745378B}" name="Columna2"/>
+  </tableColumns>
+  <tableStyleInfo name="Estilo de tabla 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{7EEAEA03-33D9-42E9-B633-0F8E22CD5A9F}" name="Tabla9" displayName="Tabla9" ref="I1:K11" totalsRowShown="0" headerRowDxfId="28" headerRowBorderDxfId="27" tableBorderDxfId="26" headerRowCellStyle="Énfasis1">
+  <autoFilter ref="I1:K11" xr:uid="{7EEAEA03-33D9-42E9-B633-0F8E22CD5A9F}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{A7FF47DC-FF63-4638-8F45-0892AC1E9865}" name=" Log  Actividad" dataCellStyle="20% - Énfasis1"/>
+    <tableColumn id="2" xr3:uid="{1B735AD7-37B5-4609-BADE-FE700E3A86CD}" name="Columna1" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{C2BAFCE9-1A8D-47E5-8E71-A4A26A5B7D4B}" name="Columna2" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="Estilo de tabla 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1283,7 +1941,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1317,6 +1975,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1351,9 +2010,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1526,50 +2186,50 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
     <col min="2" max="2" width="19.7109375" customWidth="1"/>
     <col min="3" max="3" width="25.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="80" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="78" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="C2" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="40" t="s">
-        <v>93</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="41" t="s">
-        <v>93</v>
+      <c r="B4" s="34" t="s">
+        <v>76</v>
       </c>
       <c r="C4" s="10"/>
     </row>
@@ -1583,9 +2243,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AA15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27" style="1" customWidth="1"/>
     <col min="2" max="2" width="22.140625" style="1" customWidth="1"/>
@@ -1617,447 +2277,447 @@
     <col min="28" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27">
-      <c r="A1" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="52" t="s">
-        <v>91</v>
-      </c>
-      <c r="C1" s="52" t="s">
-        <v>92</v>
-      </c>
-      <c r="E1" s="53" t="s">
-        <v>89</v>
-      </c>
-      <c r="F1" s="53" t="s">
-        <v>91</v>
-      </c>
-      <c r="G1" s="53" t="s">
-        <v>92</v>
-      </c>
-      <c r="I1" s="53" t="s">
-        <v>90</v>
-      </c>
-      <c r="J1" s="53" t="s">
-        <v>91</v>
-      </c>
-      <c r="K1" s="53" t="s">
-        <v>92</v>
-      </c>
-      <c r="M1" s="53" t="s">
-        <v>86</v>
-      </c>
-      <c r="N1" s="53" t="s">
-        <v>91</v>
-      </c>
-      <c r="O1" s="53" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q1" s="53" t="s">
-        <v>87</v>
-      </c>
-      <c r="R1" s="53" t="s">
-        <v>91</v>
-      </c>
-      <c r="S1" s="53" t="s">
-        <v>92</v>
-      </c>
-      <c r="U1" s="82" t="s">
-        <v>88</v>
-      </c>
-      <c r="V1" s="83"/>
-      <c r="W1" s="83"/>
-      <c r="Y1" s="67" t="s">
-        <v>85</v>
-      </c>
-      <c r="Z1" s="67" t="s">
-        <v>91</v>
-      </c>
-      <c r="AA1" s="67" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27">
-      <c r="A2" s="54" t="s">
-        <v>41</v>
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A1" s="44" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="44" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="44" t="s">
+        <v>75</v>
+      </c>
+      <c r="E1" s="45" t="s">
+        <v>72</v>
+      </c>
+      <c r="F1" s="45" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1" s="45" t="s">
+        <v>75</v>
+      </c>
+      <c r="I1" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="J1" s="45" t="s">
+        <v>74</v>
+      </c>
+      <c r="K1" s="45" t="s">
+        <v>75</v>
+      </c>
+      <c r="M1" s="45" t="s">
+        <v>69</v>
+      </c>
+      <c r="N1" s="45" t="s">
+        <v>74</v>
+      </c>
+      <c r="O1" s="45" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q1" s="45" t="s">
+        <v>70</v>
+      </c>
+      <c r="R1" s="45" t="s">
+        <v>74</v>
+      </c>
+      <c r="S1" s="45" t="s">
+        <v>75</v>
+      </c>
+      <c r="U1" s="80" t="s">
+        <v>71</v>
+      </c>
+      <c r="V1" s="81"/>
+      <c r="W1" s="81"/>
+      <c r="Y1" s="45" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z1" s="45" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA1" s="45" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A2" s="46" t="s">
+        <v>35</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="54" t="s">
-        <v>41</v>
+        <v>17</v>
+      </c>
+      <c r="E2" s="46" t="s">
+        <v>35</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="M2" s="54" t="s">
-        <v>41</v>
+        <v>17</v>
+      </c>
+      <c r="M2" s="46" t="s">
+        <v>35</v>
       </c>
       <c r="N2" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O2" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q2" s="64" t="s">
-        <v>41</v>
+        <v>17</v>
+      </c>
+      <c r="Q2" s="56" t="s">
+        <v>35</v>
       </c>
       <c r="R2" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="S2" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="U2" s="8" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="V2" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="W2" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y2" s="68" t="s">
-        <v>41</v>
-      </c>
-      <c r="Z2" s="69" t="s">
-        <v>22</v>
-      </c>
-      <c r="AA2" s="69" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="15">
-      <c r="A3" s="55" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="22" t="s">
-        <v>93</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="57" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y2" s="46" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z2" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA2" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" ht="15" x14ac:dyDescent="0.25">
+      <c r="A3" s="47" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="49" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="23" t="s">
         <v>1</v>
       </c>
       <c r="G3" s="9"/>
-      <c r="I3" s="78" t="s">
-        <v>11</v>
-      </c>
-      <c r="J3" s="76" t="s">
+      <c r="I3" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="J3" s="62" t="s">
         <v>1</v>
       </c>
       <c r="K3" s="2"/>
-      <c r="M3" s="55" t="s">
-        <v>11</v>
+      <c r="M3" s="47" t="s">
+        <v>10</v>
       </c>
       <c r="N3" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="O3" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q3" s="55" t="s">
-        <v>11</v>
-      </c>
-      <c r="R3" s="16" t="s">
+      <c r="O3" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q3" s="47" t="s">
+        <v>10</v>
+      </c>
+      <c r="R3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="S3" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="U3" s="19" t="s">
-        <v>11</v>
+      <c r="S3" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="U3" s="17" t="s">
+        <v>10</v>
       </c>
       <c r="V3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="W3" s="17" t="s">
+      <c r="W3" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y3" s="59" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z3" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="9"/>
+    </row>
+    <row r="4" spans="1:27" ht="15" x14ac:dyDescent="0.25">
+      <c r="A4" s="48" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" s="25"/>
+      <c r="E4" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="K4" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="M4" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="N4" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="O4" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="Y3" s="70" t="s">
+      <c r="Q4" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="Z3" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA3" s="9"/>
-    </row>
-    <row r="4" spans="1:27" ht="15">
-      <c r="A4" s="56" t="s">
+      <c r="R4" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="S4" s="16"/>
+      <c r="U4" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="V4" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="W4" s="16"/>
+      <c r="Y4" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z4" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" ht="15" x14ac:dyDescent="0.25">
+      <c r="E5" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="25" t="s">
-        <v>93</v>
-      </c>
-      <c r="C4" s="28"/>
-      <c r="E4" s="58" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="J4" s="77" t="s">
-        <v>100</v>
-      </c>
-      <c r="K4" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="M4" s="56" t="s">
-        <v>12</v>
-      </c>
-      <c r="N4" s="33" t="s">
-        <v>100</v>
-      </c>
-      <c r="O4" s="11" t="s">
+      <c r="F5" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="G5" s="25"/>
+      <c r="I5" s="63" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="57" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="58" t="s">
         <v>20</v>
       </c>
-      <c r="Q4" s="56" t="s">
-        <v>12</v>
-      </c>
-      <c r="R4" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="S4" s="18"/>
-      <c r="U4" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="V4" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="W4" s="18"/>
-      <c r="Y4" s="71" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z4" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="15">
-      <c r="E5" s="58" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" s="27" t="s">
-        <v>101</v>
-      </c>
-      <c r="G5" s="28"/>
-      <c r="I5" s="78" t="s">
-        <v>14</v>
-      </c>
-      <c r="J5" s="65" t="s">
-        <v>82</v>
-      </c>
-      <c r="K5" s="66" t="s">
-        <v>21</v>
-      </c>
-      <c r="M5" s="58" t="s">
-        <v>3</v>
-      </c>
-      <c r="N5" s="77" t="s">
-        <v>104</v>
-      </c>
-      <c r="O5" s="90"/>
-      <c r="Q5" s="56" t="s">
-        <v>14</v>
-      </c>
-      <c r="R5" s="65" t="s">
-        <v>82</v>
-      </c>
-      <c r="S5" s="66" t="s">
-        <v>21</v>
-      </c>
-      <c r="U5" s="20" t="s">
-        <v>11</v>
+      <c r="M5" s="50" t="s">
+        <v>2</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="O5" s="65"/>
+      <c r="Q5" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="R5" s="57" t="s">
+        <v>65</v>
+      </c>
+      <c r="S5" s="58" t="s">
+        <v>20</v>
+      </c>
+      <c r="U5" s="18" t="s">
+        <v>10</v>
       </c>
       <c r="V5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="W5" s="2"/>
-      <c r="Y5" s="72" t="s">
+      <c r="Y5" s="50" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z5" s="60" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA5" s="55" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" ht="15" x14ac:dyDescent="0.25">
+      <c r="E6" s="51" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="G6" s="25"/>
+      <c r="I6" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="J6" s="61" t="s">
+        <v>85</v>
+      </c>
+      <c r="K6" s="26"/>
+      <c r="M6" s="50" t="s">
+        <v>46</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="O6" s="65"/>
+      <c r="U6" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="V6" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="W6" s="26" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="15" x14ac:dyDescent="0.25">
+      <c r="E7" s="51" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="G7" s="25"/>
+      <c r="M7" s="50" t="s">
+        <v>77</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="O7" s="65"/>
+    </row>
+    <row r="8" spans="1:27" ht="15" x14ac:dyDescent="0.25">
+      <c r="E8" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="G8" s="25"/>
+      <c r="M8" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="O8" s="65"/>
+    </row>
+    <row r="9" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E9" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="G9" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="M9" s="50" t="s">
+        <v>41</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="O9" s="65"/>
+    </row>
+    <row r="10" spans="1:27" ht="15" x14ac:dyDescent="0.25">
+      <c r="E10" s="52" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="M10" s="50" t="s">
+        <v>79</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="O10" s="65"/>
+    </row>
+    <row r="11" spans="1:27" ht="15" x14ac:dyDescent="0.25">
+      <c r="E11" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="Z5" s="73" t="s">
-        <v>84</v>
-      </c>
-      <c r="AA5" s="63" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" ht="15">
-      <c r="E6" s="59" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" s="27" t="s">
-        <v>76</v>
-      </c>
-      <c r="G6" s="28"/>
-      <c r="I6" s="79" t="s">
-        <v>13</v>
-      </c>
-      <c r="J6" s="75" t="s">
-        <v>102</v>
-      </c>
-      <c r="K6" s="29"/>
-      <c r="M6" s="58" t="s">
-        <v>58</v>
-      </c>
-      <c r="N6" s="77" t="s">
-        <v>103</v>
-      </c>
-      <c r="O6" s="90"/>
-      <c r="U6" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="V6" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="W6" s="29" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="15">
-      <c r="E7" s="59" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="G7" s="28"/>
-      <c r="M7" s="58" t="s">
-        <v>94</v>
-      </c>
-      <c r="N7" s="77" t="s">
-        <v>42</v>
-      </c>
-      <c r="O7" s="90"/>
-    </row>
-    <row r="8" spans="1:27" ht="15">
-      <c r="E8" s="58" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="27" t="s">
-        <v>79</v>
-      </c>
-      <c r="G8" s="28"/>
-      <c r="M8" s="58" t="s">
-        <v>95</v>
-      </c>
-      <c r="N8" s="77" t="s">
-        <v>99</v>
-      </c>
-      <c r="O8" s="90"/>
-    </row>
-    <row r="9" spans="1:27" ht="15" customHeight="1">
-      <c r="E9" s="59" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="51" t="s">
-        <v>82</v>
-      </c>
-      <c r="G9" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="M9" s="58" t="s">
-        <v>50</v>
-      </c>
-      <c r="N9" s="77" t="s">
-        <v>97</v>
-      </c>
-      <c r="O9" s="90"/>
-    </row>
-    <row r="10" spans="1:27" ht="15">
-      <c r="E10" s="60" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" s="32" t="s">
-        <v>80</v>
-      </c>
-      <c r="G10" s="17" t="s">
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:27" ht="15" x14ac:dyDescent="0.25">
+      <c r="E12" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:27" ht="15" x14ac:dyDescent="0.25">
+      <c r="E13" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:27" ht="15" x14ac:dyDescent="0.25">
+      <c r="E14" s="54" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="G14" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="M10" s="58" t="s">
-        <v>96</v>
-      </c>
-      <c r="N10" s="77" t="s">
-        <v>98</v>
-      </c>
-      <c r="O10" s="90"/>
-    </row>
-    <row r="11" spans="1:27" ht="15">
-      <c r="E11" s="61" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="33" t="s">
-        <v>100</v>
-      </c>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:27" ht="15">
-      <c r="E12" s="61" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:27" ht="15">
-      <c r="E13" s="61" t="s">
-        <v>26</v>
-      </c>
-      <c r="F13" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:27" ht="15">
-      <c r="E14" s="62" t="s">
+    </row>
+    <row r="15" spans="1:27" ht="15" x14ac:dyDescent="0.25">
+      <c r="E15" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="F14" s="33" t="s">
-        <v>42</v>
-      </c>
-      <c r="G14" s="18" t="s">
+      <c r="F15" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="G15" s="16" t="s">
         <v>32</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="15">
-      <c r="E15" s="62" t="s">
-        <v>28</v>
-      </c>
-      <c r="F15" s="33" t="s">
-        <v>29</v>
-      </c>
-      <c r="G15" s="18" t="s">
-        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -2078,11 +2738,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:AA11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="25.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="3" style="1" customWidth="1"/>
@@ -2090,299 +2750,428 @@
     <col min="6" max="6" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="25.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="3" style="1" customWidth="1"/>
-    <col min="9" max="9" width="18.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="29.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="47.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.28515625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="21.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="82.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="2.5703125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="12.85546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="7.28515625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="21.5703125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="20" style="1" customWidth="1"/>
+    <col min="15" max="15" width="46.28515625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="9.140625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="37.42578125" style="1" customWidth="1"/>
     <col min="18" max="18" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="82.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="11.42578125" style="1"/>
+    <col min="20" max="20" width="3.28515625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="46.7109375" style="1" customWidth="1"/>
+    <col min="22" max="22" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="82.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.28515625" style="1" customWidth="1"/>
+    <col min="25" max="25" width="40.7109375" style="1" customWidth="1"/>
+    <col min="26" max="26" width="22" style="1" customWidth="1"/>
+    <col min="27" max="27" width="81.140625" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
-      <c r="A1" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="E1" s="84" t="s">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A1" s="44" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="44" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="44" t="s">
+        <v>75</v>
+      </c>
+      <c r="E1" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="F1" s="44" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1" s="44" t="s">
+        <v>75</v>
+      </c>
+      <c r="I1" s="44" t="s">
+        <v>99</v>
+      </c>
+      <c r="J1" s="44" t="s">
+        <v>74</v>
+      </c>
+      <c r="K1" s="44" t="s">
+        <v>75</v>
+      </c>
+      <c r="M1" s="44" t="s">
+        <v>100</v>
+      </c>
+      <c r="N1" s="44" t="s">
+        <v>74</v>
+      </c>
+      <c r="O1" s="44" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q1" s="44" t="s">
+        <v>101</v>
+      </c>
+      <c r="R1" s="44" t="s">
+        <v>74</v>
+      </c>
+      <c r="S1" s="44" t="s">
+        <v>75</v>
+      </c>
+      <c r="U1" s="44" t="s">
+        <v>102</v>
+      </c>
+      <c r="V1" s="44" t="s">
+        <v>74</v>
+      </c>
+      <c r="W1" s="44" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y1" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z1" s="44" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA1" s="44" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A2" s="46" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="O2" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q2" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="R2" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="S2" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="U2" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="V2" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="W2" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y2" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z2" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA2" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A3" s="66" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="I3" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="J3" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="L3" s="65"/>
+      <c r="M3" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="N3" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="O3" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q3" s="66" t="s">
+        <v>34</v>
+      </c>
+      <c r="R3" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="S3" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="U3" s="66" t="s">
+        <v>34</v>
+      </c>
+      <c r="V3" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="W3" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y3" s="66" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z3" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA3" s="13" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" ht="15" x14ac:dyDescent="0.25">
+      <c r="A4" s="67" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" s="25"/>
+      <c r="E4" s="67" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="G4" s="25"/>
+      <c r="I4" s="67" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="K4" s="2"/>
+      <c r="M4" s="59" t="s">
+        <v>89</v>
+      </c>
+      <c r="N4" s="68" t="s">
+        <v>90</v>
+      </c>
+      <c r="O4" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="U4" s="67" t="s">
         <v>38</v>
       </c>
-      <c r="F1" s="85"/>
-      <c r="G1" s="85"/>
-      <c r="I1" s="84" t="s">
-        <v>39</v>
-      </c>
-      <c r="J1" s="85"/>
-      <c r="K1" s="85"/>
-      <c r="M1" s="84" t="s">
+      <c r="V4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="W4" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y4" s="67" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z4" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA4" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" ht="15" x14ac:dyDescent="0.25">
+      <c r="I5" s="67" t="s">
+        <v>33</v>
+      </c>
+      <c r="J5" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="K5" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="N1" s="85"/>
-      <c r="O1" s="85"/>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" s="7" t="s">
+      <c r="L5" s="65"/>
+      <c r="M5" s="51" t="s">
+        <v>91</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="O5" s="16"/>
+      <c r="Y5" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="7" t="s">
+      <c r="Z5" s="25" t="s">
+        <v>103</v>
+      </c>
+      <c r="AA5" s="11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" ht="15" x14ac:dyDescent="0.25">
+      <c r="I6" s="59" t="s">
+        <v>89</v>
+      </c>
+      <c r="J6" s="68" t="s">
+        <v>90</v>
+      </c>
+      <c r="K6" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="M2" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="N2" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="O2" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
-      <c r="A3" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="35" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="I3" s="35" t="s">
-        <v>11</v>
-      </c>
-      <c r="J3" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="K3" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="M3" s="44" t="s">
-        <v>40</v>
-      </c>
-      <c r="N3" s="42" t="s">
-        <v>42</v>
-      </c>
-      <c r="O3" s="43" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
-      <c r="A4" s="36" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="E4" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="G4" s="10"/>
-      <c r="I4" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="J4" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="K4" s="2"/>
-    </row>
-    <row r="5" spans="1:15">
-      <c r="I5" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="J5" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="K5" s="18" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="I6" s="37" t="s">
-        <v>35</v>
-      </c>
-      <c r="J6" s="25" t="s">
-        <v>73</v>
-      </c>
-      <c r="K6" s="18" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="I7" s="36" t="s">
-        <v>36</v>
-      </c>
-      <c r="J7" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="K7" s="34" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
-      <c r="M9" s="84" t="s">
-        <v>45</v>
-      </c>
-      <c r="N9" s="85"/>
-      <c r="O9" s="85"/>
-    </row>
-    <row r="10" spans="1:15">
-      <c r="J10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M10" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="N10" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="O10" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
-      <c r="J11" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="M11" s="35" t="s">
-        <v>40</v>
-      </c>
-      <c r="N11" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="O11" s="17" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
-      <c r="M12" s="36" t="s">
-        <v>47</v>
-      </c>
-      <c r="N12" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="O12" s="34" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17" spans="13:15">
-      <c r="M17" s="84" t="s">
-        <v>46</v>
-      </c>
-      <c r="N17" s="85"/>
-      <c r="O17" s="85"/>
-    </row>
-    <row r="18" spans="13:15">
-      <c r="M18" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="N18" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="O18" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="13:15">
-      <c r="M19" s="35" t="s">
-        <v>40</v>
-      </c>
-      <c r="N19" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="O19" s="14" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="13:15">
-      <c r="M20" s="37" t="s">
-        <v>47</v>
-      </c>
-      <c r="N20" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="O20" s="11" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="21" spans="13:15">
-      <c r="M21" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="N21" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="O21" s="15" t="s">
-        <v>51</v>
-      </c>
+      <c r="L6" s="65"/>
+      <c r="M6" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="O6" s="2"/>
+    </row>
+    <row r="7" spans="1:27" ht="15" x14ac:dyDescent="0.25">
+      <c r="I7" s="51" t="s">
+        <v>91</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="K7" s="16"/>
+      <c r="L7" s="65"/>
+      <c r="M7" s="59" t="s">
+        <v>93</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:27" ht="15" x14ac:dyDescent="0.25">
+      <c r="I8" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="K8" s="2"/>
+      <c r="M8" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="O8" s="2"/>
+    </row>
+    <row r="9" spans="1:27" ht="15" x14ac:dyDescent="0.25">
+      <c r="I9" s="59" t="s">
+        <v>93</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="K9" s="2"/>
+      <c r="M9" s="51" t="s">
+        <v>95</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" ht="15" x14ac:dyDescent="0.25">
+      <c r="I10" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="K10" s="2"/>
+      <c r="M10" s="74"/>
+      <c r="O10" s="2"/>
+    </row>
+    <row r="11" spans="1:27" ht="15" x14ac:dyDescent="0.25">
+      <c r="I11" s="51" t="s">
+        <v>95</v>
+      </c>
+      <c r="J11" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="K11" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="L11" s="71"/>
+      <c r="M11" s="72"/>
+      <c r="N11" s="73"/>
+      <c r="O11" s="31"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="M17:O17"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="M9:O9"/>
-  </mergeCells>
+  <phoneticPr fontId="13" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="J5">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="J5" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>$J$10:$J$11</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <tableParts count="7">
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId6"/>
+    <tablePart r:id="rId7"/>
+    <tablePart r:id="rId8"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:L6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:L13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.28515625" customWidth="1"/>
+    <col min="3" max="3" width="20.28515625" customWidth="1"/>
     <col min="4" max="4" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.28515625" customWidth="1"/>
     <col min="7" max="7" width="49" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.28515625" bestFit="1" customWidth="1"/>
@@ -2390,155 +3179,176 @@
     <col min="12" max="12" width="17.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12">
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-    </row>
-    <row r="2" spans="2:12">
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="86" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="44" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="44" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="44" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="G1" s="44" t="s">
+        <v>74</v>
+      </c>
+      <c r="H1" s="44" t="s">
+        <v>75</v>
+      </c>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="46" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="38"/>
+      <c r="F2" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="38"/>
+      <c r="J2" s="82" t="s">
+        <v>45</v>
+      </c>
+      <c r="K2" s="82"/>
+      <c r="L2" s="39" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="66" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" s="41" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" s="69" t="s">
+        <v>48</v>
+      </c>
+      <c r="I3" s="38"/>
+      <c r="J3" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="K3" s="41" t="s">
+        <v>49</v>
+      </c>
+      <c r="L3" s="83" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="67" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" s="25"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="40" t="s">
+        <v>50</v>
+      </c>
+      <c r="G4" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="H4" s="70"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="40" t="s">
+        <v>50</v>
+      </c>
+      <c r="K4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="L4" s="84"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D5" s="85"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="40" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5" s="42" t="s">
+        <v>54</v>
+      </c>
+      <c r="H5" s="70"/>
+      <c r="I5" s="38"/>
+      <c r="J5" s="40" t="s">
+        <v>53</v>
+      </c>
+      <c r="K5" s="42" t="s">
         <v>55</v>
       </c>
-      <c r="G2" s="86"/>
-      <c r="H2" s="46" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="45"/>
-      <c r="J2" s="86" t="s">
+      <c r="L5" s="84"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B6" s="38"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="76" t="s">
         <v>56</v>
       </c>
-      <c r="K2" s="86"/>
-      <c r="L2" s="46" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12">
-      <c r="B3" s="86" t="s">
+      <c r="G6" s="77" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="86"/>
-      <c r="D3" s="46" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="45"/>
-      <c r="F3" s="47" t="s">
+      <c r="H6" s="70"/>
+      <c r="I6" s="38"/>
+      <c r="J6" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="K6" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="G3" s="48" t="s">
-        <v>59</v>
-      </c>
-      <c r="H3" s="87" t="s">
-        <v>60</v>
-      </c>
-      <c r="I3" s="45"/>
-      <c r="J3" s="47" t="s">
-        <v>58</v>
-      </c>
-      <c r="K3" s="48" t="s">
-        <v>61</v>
-      </c>
-      <c r="L3" s="87" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12">
-      <c r="B4" s="47" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" s="49" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="87" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" s="45"/>
-      <c r="F4" s="47" t="s">
-        <v>63</v>
-      </c>
-      <c r="G4" s="48" t="s">
-        <v>64</v>
-      </c>
-      <c r="H4" s="88"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="47" t="s">
-        <v>63</v>
-      </c>
-      <c r="K4" s="48" t="s">
-        <v>65</v>
-      </c>
-      <c r="L4" s="88"/>
-    </row>
-    <row r="5" spans="2:12">
-      <c r="B5" s="47" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" s="49" t="s">
-        <v>81</v>
-      </c>
-      <c r="D5" s="89"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="G5" s="50" t="s">
-        <v>68</v>
-      </c>
-      <c r="H5" s="88"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="K5" s="50" t="s">
-        <v>69</v>
-      </c>
-      <c r="L5" s="88"/>
-    </row>
-    <row r="6" spans="2:12">
-      <c r="B6" s="45"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="47" t="s">
-        <v>70</v>
-      </c>
-      <c r="G6" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="H6" s="89"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="47" t="s">
-        <v>70</v>
-      </c>
-      <c r="K6" s="48" t="s">
-        <v>72</v>
-      </c>
-      <c r="L6" s="89"/>
+      <c r="L6" s="85"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G13" s="75"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="F2:G2"/>
+  <mergeCells count="3">
     <mergeCell ref="J2:K2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="H3:H6"/>
     <mergeCell ref="L3:L6"/>
     <mergeCell ref="D4:D5"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="G5" r:id="rId1"/>
-    <hyperlink ref="K5" r:id="rId2"/>
+    <hyperlink ref="G5" r:id="rId1" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
+    <hyperlink ref="K5" r:id="rId2" xr:uid="{00000000-0004-0000-0300-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="2">
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+  </tableParts>
 </worksheet>
 </file>